--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -196,7 +196,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,12 +206,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,17 +255,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -70,7 +76,19 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
+    <t>10 Л. ДOБABKA ADBLUE</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>14:24</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -488,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -501,10 +519,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -538,22 +558,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>120.01</v>
@@ -570,25 +596,31 @@
       <c r="J2">
         <v>188.42</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>111741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -605,25 +637,31 @@
       <c r="J3">
         <v>156</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>195057</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -640,25 +678,31 @@
       <c r="J4">
         <v>142.74</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>195077</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>120.01</v>
@@ -675,13 +719,19 @@
       <c r="J5">
         <v>187.22</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M5">
+        <v>198094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -689,18 +739,18 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>7</v>
@@ -709,9 +759,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="6">
         <v>340.02</v>
@@ -729,9 +779,9 @@
         <v>531.64</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="6">
         <v>6</v>
@@ -749,9 +799,9 @@
         <v>142.74</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9">
         <v>346.02</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -64,6 +58,12 @@
     <t>2026-06-12</t>
   </si>
   <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
@@ -76,19 +76,25 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>10 Л. ДOБABKA ADBLUE</t>
-  </si>
-  <si>
-    <t>14:01</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>14:24</t>
+    <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
+  </si>
+  <si>
+    <t>2026-06-01 14:01:26</t>
+  </si>
+  <si>
+    <t>2026-06-08 08:43:16</t>
+  </si>
+  <si>
+    <t>2026-06-08 09:13:06</t>
+  </si>
+  <si>
+    <t>2026-06-12 14:24:03</t>
+  </si>
+  <si>
+    <t>2026-06-18 09:54:13</t>
+  </si>
+  <si>
+    <t>2026-06-24 10:02:30</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -506,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -519,12 +525,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,16 +562,10 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -599,16 +597,10 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>111741</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -640,16 +632,10 @@
       <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>195057</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -681,16 +667,10 @@
       <c r="K4" t="s">
         <v>23</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>195077</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -722,104 +702,168 @@
       <c r="K5" t="s">
         <v>24</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>198094</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>120</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H6">
+        <v>182.4</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J6">
+        <v>186</v>
+      </c>
+      <c r="K6" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>120</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H7">
+        <v>177.6</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J7">
+        <v>181.2</v>
+      </c>
+      <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="6">
-        <v>340.02</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.5336</v>
-      </c>
-      <c r="E10" s="6">
-        <v>521.4400000000001</v>
-      </c>
-      <c r="F10" s="6">
-        <v>531.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="6">
+        <v>580.02</v>
+      </c>
+      <c r="C12" s="6">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.5197</v>
+      </c>
+      <c r="E12" s="6">
+        <v>881.4400000000001</v>
+      </c>
+      <c r="F12" s="6">
+        <v>898.84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B13" s="6">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C13" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D13" s="7">
         <v>23.79</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E13" s="6">
         <v>142.74</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F13" s="6">
         <v>142.74</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="9">
-        <v>346.02</v>
-      </c>
-      <c r="C12" s="9">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>664.1799999999999</v>
-      </c>
-      <c r="F12" s="9">
-        <v>674.38</v>
+    <row r="14" spans="1:11">
+      <c r="A14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="9">
+        <v>586.02</v>
+      </c>
+      <c r="C14" s="9">
+        <v>6</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="9">
+        <v>1024.18</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1041.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="47">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -64,7 +73,10 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>ТУБА</t>
@@ -79,22 +91,52 @@
     <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
   </si>
   <si>
-    <t>2026-06-01 14:01:26</t>
-  </si>
-  <si>
-    <t>2026-06-08 08:43:16</t>
-  </si>
-  <si>
-    <t>2026-06-08 09:13:06</t>
-  </si>
-  <si>
-    <t>2026-06-12 14:24:03</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:54:13</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:02:30</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>14:01:00</t>
+  </si>
+  <si>
+    <t>09:13:00</t>
+  </si>
+  <si>
+    <t>08:43:00</t>
+  </si>
+  <si>
+    <t>14:24:00</t>
+  </si>
+  <si>
+    <t>09:54:00</t>
+  </si>
+  <si>
+    <t>10:02:00</t>
+  </si>
+  <si>
+    <t>15:06:00</t>
+  </si>
+  <si>
+    <t>3232713729 3232713729</t>
+  </si>
+  <si>
+    <t>3233015888 3233015888</t>
+  </si>
+  <si>
+    <t>3233039084 3233039084</t>
+  </si>
+  <si>
+    <t>3233241357 3233241357</t>
+  </si>
+  <si>
+    <t>3233523430 3233523430</t>
+  </si>
+  <si>
+    <t>3233805524 3233805524</t>
+  </si>
+  <si>
+    <t>3233909955 3233909955</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -512,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,14 +563,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,308 +607,415 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>120.01</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1.54</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>184.82</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>188.42</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>23.79</v>
+      </c>
+      <c r="I3" s="1">
+        <v>142.74</v>
+      </c>
+      <c r="J3">
+        <v>23.79</v>
+      </c>
+      <c r="K3" s="1">
+        <v>142.74</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>1.53</v>
+      </c>
+      <c r="I4" s="1">
+        <v>153</v>
+      </c>
+      <c r="J4">
+        <v>1.56</v>
+      </c>
+      <c r="K4" s="1">
+        <v>156</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H3">
-        <v>153</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J3">
-        <v>156</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4" s="1">
-        <v>23.79</v>
-      </c>
-      <c r="H4">
-        <v>142.74</v>
-      </c>
-      <c r="I4" s="1">
-        <v>23.79</v>
-      </c>
-      <c r="J4">
-        <v>142.74</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="E5" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
       </c>
       <c r="F5">
         <v>120.01</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
         <v>1.53</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>183.62</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>187.22</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>120</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
         <v>1.52</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>182.4</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.55</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>186</v>
       </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>120</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7">
         <v>1.48</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>177.6</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.51</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>181.2</v>
       </c>
-      <c r="K7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>1.47</v>
+      </c>
+      <c r="I8" s="1">
+        <v>147</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>150</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="6">
+        <v>680.02</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.5124</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1028.44</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1048.84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="6">
+        <v>6</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>23.79</v>
+      </c>
+      <c r="E14" s="6">
+        <v>142.74</v>
+      </c>
+      <c r="F14" s="6">
+        <v>142.74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="9">
+        <v>686.02</v>
+      </c>
+      <c r="C15" s="9">
         <v>7</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6">
-        <v>580.02</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.5197</v>
-      </c>
-      <c r="E12" s="6">
-        <v>881.4400000000001</v>
-      </c>
-      <c r="F12" s="6">
-        <v>898.84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="6">
-        <v>6</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7">
-        <v>23.79</v>
-      </c>
-      <c r="E13" s="6">
-        <v>142.74</v>
-      </c>
-      <c r="F13" s="6">
-        <v>142.74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="9">
-        <v>586.02</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>1024.18</v>
-      </c>
-      <c r="F14" s="9">
-        <v>1041.58</v>
+      <c r="D15" s="7"/>
+      <c r="E15" s="9">
+        <v>1171.18</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1191.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,15 +55,6 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
     <t>2026-06-18</t>
   </si>
   <si>
@@ -76,7 +64,7 @@
     <t>2026-06-26</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>ТУБА</t>
@@ -88,55 +76,13 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>14:01:00</t>
-  </si>
-  <si>
-    <t>09:13:00</t>
-  </si>
-  <si>
-    <t>08:43:00</t>
-  </si>
-  <si>
-    <t>14:24:00</t>
-  </si>
-  <si>
-    <t>09:54:00</t>
-  </si>
-  <si>
-    <t>10:02:00</t>
-  </si>
-  <si>
-    <t>15:06:00</t>
-  </si>
-  <si>
-    <t>3232713729 3232713729</t>
-  </si>
-  <si>
-    <t>3233015888 3233015888</t>
-  </si>
-  <si>
-    <t>3233039084 3233039084</t>
-  </si>
-  <si>
-    <t>3233241357 3233241357</t>
-  </si>
-  <si>
-    <t>3233523430 3233523430</t>
-  </si>
-  <si>
-    <t>3233805524 3233805524</t>
-  </si>
-  <si>
-    <t>3233909955 3233909955</t>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>15:06</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -554,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -563,17 +509,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -613,409 +558,201 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>120</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>182.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>186</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>201200</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>120</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>177.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>181.2</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>120.01</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>1.54</v>
-      </c>
-      <c r="I2" s="1">
-        <v>184.82</v>
-      </c>
-      <c r="J2">
-        <v>1.57</v>
-      </c>
-      <c r="K2" s="1">
-        <v>188.42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2">
+      <c r="L3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>34</v>
+      <c r="M3">
+        <v>118479</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23.79</v>
-      </c>
-      <c r="I3" s="1">
-        <v>142.74</v>
-      </c>
-      <c r="J3">
-        <v>23.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>142.74</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H4">
+        <v>147</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J4">
+        <v>150</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>205933</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H4">
-        <v>1.53</v>
-      </c>
-      <c r="I4" s="1">
-        <v>153</v>
-      </c>
-      <c r="J4">
-        <v>1.56</v>
-      </c>
-      <c r="K4" s="1">
-        <v>156</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>120.01</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>1.53</v>
-      </c>
-      <c r="I5" s="1">
-        <v>183.62</v>
-      </c>
-      <c r="J5">
-        <v>1.56</v>
-      </c>
-      <c r="K5" s="1">
-        <v>187.22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="6">
+        <v>340</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.4912</v>
+      </c>
+      <c r="E9" s="6">
+        <v>507</v>
+      </c>
+      <c r="F9" s="6">
+        <v>517.2</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>120</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>1.52</v>
-      </c>
-      <c r="I6" s="1">
-        <v>182.4</v>
-      </c>
-      <c r="J6">
-        <v>1.55</v>
-      </c>
-      <c r="K6" s="1">
-        <v>186</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>120</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>1.48</v>
-      </c>
-      <c r="I7" s="1">
-        <v>177.6</v>
-      </c>
-      <c r="J7">
-        <v>1.51</v>
-      </c>
-      <c r="K7" s="1">
-        <v>181.2</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8">
-        <v>1.47</v>
-      </c>
-      <c r="I8" s="1">
-        <v>147</v>
-      </c>
-      <c r="J8">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>150</v>
-      </c>
-      <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="6">
-        <v>680.02</v>
-      </c>
-      <c r="C13" s="6">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.5124</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1028.44</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1048.84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="6">
-        <v>6</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>23.79</v>
-      </c>
-      <c r="E14" s="6">
-        <v>142.74</v>
-      </c>
-      <c r="F14" s="6">
-        <v>142.74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="9">
-        <v>686.02</v>
-      </c>
-      <c r="C15" s="9">
-        <v>7</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>1171.18</v>
-      </c>
-      <c r="F15" s="9">
-        <v>1191.58</v>
+    <row r="10" spans="1:13">
+      <c r="A10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="9">
+        <v>340</v>
+      </c>
+      <c r="C10" s="9">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9">
+        <v>507</v>
+      </c>
+      <c r="F10" s="9">
+        <v>517.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -55,16 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>ТУБА</t>
@@ -76,13 +73,10 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>09:54</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>15:06</t>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>09:13</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -500,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -564,40 +558,40 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>120</v>
       </c>
       <c r="G2" s="1">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="H2">
-        <v>182.4</v>
+        <v>176.4</v>
       </c>
       <c r="I2" s="1">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="J2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>201200</v>
+        <v>123270</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -605,154 +599,113 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
       <c r="F3">
-        <v>120</v>
+        <v>170.05</v>
       </c>
       <c r="G3" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H3">
-        <v>177.6</v>
+        <v>248.27</v>
       </c>
       <c r="I3" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J3">
-        <v>181.2</v>
+        <v>253.37</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>118479</v>
+        <v>216477</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H4">
-        <v>147</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J4">
-        <v>150</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>205933</v>
-      </c>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6">
+        <v>290.05</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.4641</v>
+      </c>
+      <c r="E8" s="6">
+        <v>424.67</v>
+      </c>
+      <c r="F8" s="6">
+        <v>433.37</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="6">
-        <v>340</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.4912</v>
-      </c>
-      <c r="E9" s="6">
-        <v>507</v>
-      </c>
-      <c r="F9" s="6">
-        <v>517.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9">
-        <v>340</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>507</v>
-      </c>
-      <c r="F10" s="9">
-        <v>517.2</v>
+      <c r="A9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="9">
+        <v>290.05</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>424.67</v>
+      </c>
+      <c r="F9" s="9">
+        <v>433.37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -52,16 +52,13 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>2026-07-07</t>
   </si>
   <si>
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>ТУБА</t>
@@ -73,10 +70,10 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>09:13</t>
+    <t>2026-07-07 09:39:10</t>
+  </si>
+  <si>
+    <t>2026-07-14 09:13:07</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -494,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -507,12 +504,11 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,25 +545,22 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
       </c>
       <c r="F2">
         <v>120</v>
@@ -585,30 +578,27 @@
         <v>180</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>123270</v>
-      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
       </c>
       <c r="F3">
         <v>170.05</v>
@@ -626,18 +616,15 @@
         <v>253.37</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>216477</v>
-      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -645,18 +632,18 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>7</v>
@@ -665,9 +652,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:12">
       <c r="A8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="6">
         <v>290.05</v>
@@ -685,9 +672,9 @@
         <v>433.37</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:12">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="9">
         <v>290.05</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,25 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-07</t>
   </si>
   <si>
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>ТУБА</t>
@@ -70,10 +85,43 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-07 09:39:10</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:13:07</t>
+    <t>4 Л. AHTИФPИЗ ГOTOB ЗA УПOTPEБA (-37°C)</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>09:13:00</t>
+  </si>
+  <si>
+    <t>10:03:00</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>13:49:00</t>
+  </si>
+  <si>
+    <t>3234430486 3234430486</t>
+  </si>
+  <si>
+    <t>3234782352 3234782352</t>
+  </si>
+  <si>
+    <t>3234860390 3234860390</t>
+  </si>
+  <si>
+    <t>3235137201 3235137201</t>
+  </si>
+  <si>
+    <t>3235482119 3235482119</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -491,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,15 +548,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,154 +595,324 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>120</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>1.47</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>176.4</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>180</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>170.05</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>248.27</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.49</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>253.37</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>15.89</v>
+      </c>
+      <c r="I4" s="1">
+        <v>63.56</v>
+      </c>
+      <c r="J4">
+        <v>15.89</v>
+      </c>
+      <c r="K4" s="1">
+        <v>63.56</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="F5">
+        <v>120</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="1">
+        <v>180</v>
+      </c>
+      <c r="J5">
+        <v>1.53</v>
+      </c>
+      <c r="K5" s="1">
+        <v>183.6</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>120.01</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>1.53</v>
+      </c>
+      <c r="I6" s="1">
+        <v>183.62</v>
+      </c>
+      <c r="J6">
+        <v>1.56</v>
+      </c>
+      <c r="K6" s="1">
+        <v>187.22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6">
+        <v>530.0599999999999</v>
+      </c>
+      <c r="C11" s="6">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.4872</v>
+      </c>
+      <c r="E11" s="6">
+        <v>788.29</v>
+      </c>
+      <c r="F11" s="6">
+        <v>804.1900000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6">
-        <v>290.05</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.4641</v>
-      </c>
-      <c r="E8" s="6">
-        <v>424.67</v>
-      </c>
-      <c r="F8" s="6">
-        <v>433.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="9">
-        <v>290.05</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>424.67</v>
-      </c>
-      <c r="F9" s="9">
-        <v>433.37</v>
+      <c r="B12" s="6">
+        <v>4</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>15.89</v>
+      </c>
+      <c r="E12" s="6">
+        <v>63.56</v>
+      </c>
+      <c r="F12" s="6">
+        <v>63.56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="9">
+        <v>534.0599999999999</v>
+      </c>
+      <c r="C13" s="9">
+        <v>5</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9">
+        <v>851.85</v>
+      </c>
+      <c r="F13" s="9">
+        <v>867.75</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -148,7 +148,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="7">
-        <v>1.4872</v>
+        <v>1.487171</v>
       </c>
       <c r="E11" s="6">
         <v>788.29</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -539,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -552,13 +555,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -601,230 +604,248 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>120</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.359</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="J2">
+        <v>176.4</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="1">
+        <v>180</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>170.047</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>1.369</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="J3">
+        <v>248.26862</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L3" s="1">
+        <v>253.37003</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-      <c r="H2">
-        <v>1.47</v>
-      </c>
-      <c r="I2" s="1">
-        <v>176.4</v>
-      </c>
-      <c r="J2">
-        <v>1.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>180</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>170.05</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.46</v>
-      </c>
-      <c r="I3" s="1">
-        <v>248.27</v>
-      </c>
-      <c r="J3">
-        <v>1.49</v>
-      </c>
-      <c r="K3" s="1">
-        <v>253.37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>15.89</v>
       </c>
       <c r="I4" s="1">
+        <v>15.89</v>
+      </c>
+      <c r="J4">
         <v>63.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>15.89</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>63.56</v>
       </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>120</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5">
+        <v>1.389</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.5</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>180</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>1.53</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>183.6</v>
       </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>120.01</v>
+        <v>120.013</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6">
+        <v>1.441</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.53</v>
       </c>
-      <c r="I6" s="1">
-        <v>183.62</v>
-      </c>
       <c r="J6">
+        <v>183.61989</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.56</v>
       </c>
-      <c r="K6" s="1">
-        <v>187.22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>187.22028</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -832,29 +853,29 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="6">
         <v>530.0599999999999</v>
@@ -863,7 +884,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="7">
-        <v>1.487171</v>
+        <v>1.487168</v>
       </c>
       <c r="E11" s="6">
         <v>788.29</v>
@@ -872,9 +893,9 @@
         <v>804.1900000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="6">
         <v>4</v>
@@ -892,9 +913,9 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="9">
         <v>534.0599999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -150,8 +147,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -244,10 +241,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -555,13 +552,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -604,248 +601,230 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
       </c>
       <c r="F2">
         <v>120</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I2" s="1">
-        <v>1.47</v>
+        <v>176.4</v>
       </c>
       <c r="J2">
-        <v>176.4</v>
+        <v>1.5</v>
       </c>
       <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
         <v>180</v>
       </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
       </c>
       <c r="F3">
         <v>170.047</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>1.369</v>
+        <v>1.46</v>
       </c>
       <c r="I3" s="1">
-        <v>1.46</v>
+        <v>248.269</v>
       </c>
       <c r="J3">
-        <v>248.26862</v>
+        <v>1.49</v>
       </c>
       <c r="K3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L3" s="1">
-        <v>253.37003</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3">
+        <v>253.37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>15.89</v>
       </c>
       <c r="I4" s="1">
+        <v>63.56</v>
+      </c>
+      <c r="J4">
         <v>15.89</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>63.56</v>
       </c>
-      <c r="K4" s="1">
-        <v>15.89</v>
-      </c>
-      <c r="L4" s="1">
-        <v>63.56</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
       </c>
       <c r="F5">
         <v>120</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I5" s="1">
-        <v>1.5</v>
+        <v>180</v>
       </c>
       <c r="J5">
-        <v>180</v>
+        <v>1.53</v>
       </c>
       <c r="K5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L5" s="1">
         <v>183.6</v>
       </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
       <c r="F6">
         <v>120.013</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I6" s="1">
-        <v>1.53</v>
+        <v>183.62</v>
       </c>
       <c r="J6">
-        <v>183.61989</v>
+        <v>1.56</v>
       </c>
       <c r="K6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L6" s="1">
-        <v>187.22028</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6">
+        <v>187.22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -853,69 +832,69 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="6">
         <v>530.0599999999999</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>4</v>
       </c>
       <c r="D11" s="7">
-        <v>1.487168</v>
-      </c>
-      <c r="E11" s="6">
-        <v>788.29</v>
-      </c>
-      <c r="F11" s="6">
+        <v>1.487</v>
+      </c>
+      <c r="E11" s="7">
+        <v>788.289</v>
+      </c>
+      <c r="F11" s="7">
         <v>804.1900000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="6">
         <v>4</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="7">
         <v>15.89</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>63.56</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>63.56</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="9">
         <v>534.0599999999999</v>
@@ -925,7 +904,7 @@
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="9">
-        <v>851.85</v>
+        <v>851.849</v>
       </c>
       <c r="F13" s="9">
         <v>867.75</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -637,10 +637,10 @@
         <v>27</v>
       </c>
       <c r="H2" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I2" s="1">
-        <v>171.48</v>
+        <v>182.4</v>
       </c>
       <c r="J2" s="1">
         <v>1.55</v>
@@ -681,10 +681,10 @@
         <v>27</v>
       </c>
       <c r="H3" s="1">
-        <v>1.409</v>
+        <v>1.52</v>
       </c>
       <c r="I3" s="1">
-        <v>112.776</v>
+        <v>121.661</v>
       </c>
       <c r="J3" s="1">
         <v>1.55</v>
@@ -813,10 +813,10 @@
         <v>27</v>
       </c>
       <c r="H6" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I6" s="1">
-        <v>172.68</v>
+        <v>184.8</v>
       </c>
       <c r="J6" s="1">
         <v>1.57</v>
@@ -963,10 +963,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="8">
-        <v>1.42775</v>
+        <v>1.5275</v>
       </c>
       <c r="E13" s="6">
-        <v>456.94</v>
+        <v>488.86</v>
       </c>
       <c r="F13" s="6">
         <v>498.46</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="10">
-        <v>701.21</v>
+        <v>733.13</v>
       </c>
       <c r="F18" s="10">
         <v>742.73</v>
